--- a/src/attributions/attributions_ig_traj_485.xlsx
+++ b/src/attributions/attributions_ig_traj_485.xlsx
@@ -999,19 +999,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.007711719895713385</v>
+        <v>-0.05027070080546003</v>
       </c>
       <c r="B2" t="n">
-        <v>0.09664497298127088</v>
+        <v>0.05786825469008225</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.007527144341520643</v>
+        <v>-0.002457330084562361</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1020,16 +1020,16 @@
         <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.01576259089039712</v>
+        <v>-0.03279701059133872</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05032946559913689</v>
+        <v>0.07694580149692137</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,67 +1038,67 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.05810804764532224</v>
+        <v>-0.03024370798276705</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02396302693444838</v>
+        <v>0.05341914120883734</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2002109156741753</v>
+        <v>0.02686504693139468</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1242801810552251</v>
+        <v>-0.01182553981853278</v>
       </c>
       <c r="X2" t="n">
         <v>-0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.07013015570561844</v>
+        <v>0.04439543187272565</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1500858127403027</v>
+        <v>0.02185715021279022</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1047584962430614</v>
+        <v>-0.04361587222461203</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
@@ -1107,10 +1107,10 @@
         <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.0183886724533078</v>
+        <v>0.0502071941773824</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.07433158122545022</v>
+        <v>0.05715674062920023</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,79 +1119,79 @@
         <v>-0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.06722186885920604</v>
+        <v>0.06820253249770825</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.07312292876453685</v>
+        <v>-0.04642850799323812</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.2353873040722437</v>
+        <v>0.2353854568661668</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2468585807388602</v>
+        <v>-0.08806185246859911</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.03417214868953432</v>
+        <v>-0.0589786547302863</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.01702357416004882</v>
+        <v>-0.03589671074376458</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.2061671574659157</v>
+        <v>-0.02955714276520677</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0.02307527084189318</v>
+        <v>0.05605145392568987</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.08466767872046149</v>
+        <v>0.06646426951508522</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
@@ -1200,34 +1200,34 @@
         <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.008660601580964291</v>
+        <v>0.06347077855814588</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
         <v>-0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.03003478679508885</v>
+        <v>0.0005638175301969624</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.09421999628427767</v>
+        <v>0.1396250870897235</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.04916046721841068</v>
+        <v>0.01277662953401273</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1242,10 +1242,10 @@
         <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.002656929578422731</v>
+        <v>0.03497409840777145</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.0768136838706846</v>
+        <v>-0.08338099812660862</v>
       </c>
       <c r="CF2" t="n">
         <v>-0</v>
@@ -1254,34 +1254,34 @@
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.02339584593831434</v>
+        <v>-0.01695300955886454</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
         <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.02524257612632418</v>
+        <v>-0.03039078232320513</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.02427666199416171</v>
+        <v>-0.07465315155244705</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.02124293617572175</v>
+        <v>-0.03283176214969175</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
@@ -1290,43 +1290,43 @@
         <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.007505588581611729</v>
+        <v>0.01032900532297702</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.08527128092870592</v>
+        <v>-0.08573354638641244</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.06339228933132064</v>
+        <v>-0.05010428718100007</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0.002732342293847493</v>
+        <v>0.001224382271670777</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1118582141945404</v>
+        <v>-0.1518885934952312</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
@@ -1335,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.2097953025935675</v>
+        <v>-0.002613233490004047</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
@@ -1350,52 +1350,52 @@
         <v>-0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0.02073027002953919</v>
+        <v>0.007369199756122879</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.0004565281287520245</v>
+        <v>-0.03331087108887861</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.04041834564333152</v>
+        <v>-0.07926580469537804</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.03999515717437733</v>
+        <v>0.00318085244861076</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1739641552038891</v>
+        <v>-0.1125709651091263</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.03395729068268898</v>
+        <v>0.006820588277716553</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0.03108291444283885</v>
+        <v>0.04591115358892662</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.01746427715585797</v>
+        <v>-0.01797744626626605</v>
       </c>
       <c r="EH2" t="n">
         <v>-0</v>
@@ -1416,37 +1416,37 @@
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.1358363875196404</v>
+        <v>-0.05861624780937286</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
         <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0.002208191932639641</v>
+        <v>-0.007416607760719612</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.06091587297490345</v>
+        <v>-0.04628427786166758</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
         <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.07281093332707814</v>
+        <v>-0.007242992758995486</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
         <v>0</v>
@@ -1455,49 +1455,49 @@
         <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0.03989910079487719</v>
+        <v>0.01747547194434303</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.1000251029649604</v>
+        <v>-0.1320628707936563</v>
       </c>
       <c r="EZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.05273543225746851</v>
+        <v>-0.0445251322944516</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
         <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.009425193557870748</v>
+        <v>0.06903934125546042</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.03302401008566198</v>
+        <v>0.07305956767858697</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.01407594843587816</v>
+        <v>-0.003979728643442976</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
@@ -1509,55 +1509,55 @@
         <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.05001048983345221</v>
+        <v>0.05397331317883349</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.07088287074915378</v>
+        <v>0.02554435547582598</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.123315241871889</v>
+        <v>0.1359173183330395</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0.04362855057594177</v>
+        <v>0.1007498254361407</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.0197934183993164</v>
+        <v>-0.06017204612947645</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
         <v>0</v>
@@ -2140,22 +2140,22 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4295398825114124</v>
+        <v>0.2284255818275716</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.07055517720623845</v>
+        <v>-0.08654632364333836</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02924064670068365</v>
+        <v>-0.03708638841493687</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -2167,22 +2167,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2527465283236312</v>
+        <v>0.1797583082218582</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1150097877409061</v>
+        <v>-0.1215698413049196</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.02452067261711428</v>
+        <v>-0.05405702724377783</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -2194,103 +2194,103 @@
         <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2652146102658319</v>
+        <v>0.1272147757230642</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07701870185707578</v>
+        <v>-0.0008136953902910828</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1880149844290747</v>
+        <v>-0.0148262051450132</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2612996249455368</v>
+        <v>-0.07012079741001249</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.04801898502074541</v>
+        <v>-0.1919021012740224</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.04100476996030122</v>
+        <v>-0.03384413086236681</v>
       </c>
       <c r="AG4" t="n">
         <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.02536499574910859</v>
+        <v>0.1394743899845105</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.1114858278890556</v>
+        <v>-0.06501552694457252</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.1020278156704</v>
+        <v>0.09456411154269542</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.7868017762713465</v>
+        <v>0.4023113501629019</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.07587067699530223</v>
+        <v>-0.2542084279254802</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.4612198687898371</v>
+        <v>-0.217033523284536</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>-0</v>
@@ -2299,22 +2299,22 @@
         <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1121403783332236</v>
+        <v>0.08248338852269717</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.1289208405348872</v>
+        <v>-0.08324126829461799</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.1894737246208062</v>
+        <v>-0.01344397543701511</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
@@ -2326,25 +2326,25 @@
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.1221858036156799</v>
+        <v>-0.03810790760655802</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.767626481643095e-10</v>
+        <v>4.897020086191953e-11</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.3627527395404165</v>
+        <v>0.0545197275124175</v>
       </c>
       <c r="BQ4" t="n">
         <v>-0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2353,52 +2353,52 @@
         <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.3314335996888412</v>
+        <v>0.2628796854703591</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.03812878869597883</v>
+        <v>-0.0893673824412184</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1016000415434852</v>
+        <v>-0.02788365799273942</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.2473524091341426</v>
+        <v>-0.1688374784074669</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0.01452761040538948</v>
+        <v>0.1572884013975933</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.05581556143273184</v>
+        <v>0.001715174458022622</v>
       </c>
       <c r="CI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
@@ -2407,52 +2407,52 @@
         <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.0270434211346889</v>
+        <v>-0.1185427566445343</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.115831799678199</v>
+        <v>0.08881609683997298</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1123038267504931</v>
+        <v>0.01622952531877004</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.2260298250207639</v>
+        <v>-0.1801115639656413</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.05403141901914638</v>
+        <v>0.1636334195810802</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.06738719738784434</v>
+        <v>0.01060843862814282</v>
       </c>
       <c r="DA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
@@ -2464,16 +2464,16 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.1156553846466708</v>
+        <v>-0.1666447426324199</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.05855109504040909</v>
+        <v>0.1832333851988883</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.1911794370244226</v>
+        <v>0.0004218618285514639</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
@@ -2488,106 +2488,106 @@
         <v>-0</v>
       </c>
       <c r="DN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.118249886418029</v>
+        <v>-0.06718592031016518</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.2709589676503018</v>
+        <v>0.07423475727865922</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.08616525686769166</v>
+        <v>0.05052174453595087</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.1225060290689824</v>
+        <v>0.02706691509467247</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.04411026477509196</v>
+        <v>0.1227256623210858</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.06892368732486868</v>
+        <v>-0.05007189489716708</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.1434285525449337</v>
+        <v>-0.1425183538897887</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0066408183077704</v>
+        <v>0.1186897749083846</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.08952128040064201</v>
+        <v>0.01374419436928751</v>
       </c>
       <c r="EK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.1909119703474684</v>
+        <v>-0.1502233346102777</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.2486707418813848</v>
+        <v>-0.07038049220764926</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.2251872984602815</v>
+        <v>-0.06522433687754632</v>
       </c>
       <c r="ET4" t="n">
         <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2596,25 +2596,25 @@
         <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.2393605048861596</v>
+        <v>-0.1966931227231954</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>-0.01323379746961791</v>
+        <v>0.1879145754394511</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.05093191760861264</v>
+        <v>-0.01529071771053068</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
@@ -2626,79 +2626,79 @@
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01723553268831045</v>
+        <v>-0.1191849023545702</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.08644886389708706</v>
+        <v>0.08799744564248438</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.06415850967561038</v>
+        <v>-0.03428106425250743</v>
       </c>
       <c r="FL4" t="n">
         <v>-0</v>
       </c>
       <c r="FM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN4" t="n">
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.006897810136193414</v>
+        <v>-0.09634560561180319</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.1316279746131354</v>
+        <v>0.2369927293001087</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.03607125012628522</v>
+        <v>0.303376147871161</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX4" t="n">
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.02669730873104775</v>
+        <v>-0.1468813358345427</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.1261622648235921</v>
+        <v>0.04546544477679775</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>-0</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.01239222425840961</v>
+        <v>-0.02827369542700293</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1704066924567438</v>
+        <v>0.09573688981732427</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02012677007158306</v>
+        <v>0.001314219325148484</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01007485518590003</v>
+        <v>-0.01554521189744919</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1335435315074935</v>
+        <v>0.09832162236226502</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0007054673130877844</v>
+        <v>-0.01325123228807215</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,22 +2760,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04160394308214947</v>
+        <v>0.0157035870814595</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2636873249760177</v>
+        <v>0.03144321523576626</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2282910007343425</v>
+        <v>0.002343978837556823</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2787,52 +2787,52 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1005176837370854</v>
+        <v>-0.01494763433388617</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1784999377277599</v>
+        <v>-0.009066860300495441</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.0006227493212707233</v>
+        <v>0.00997690741604372</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.04622804201817345</v>
+        <v>-0.01034083021148982</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.09699234114298468</v>
+        <v>0.07707609085434396</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.1447674315884988</v>
+        <v>0.0706368548273722</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
@@ -2841,10 +2841,10 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.142897356243245</v>
+        <v>-0.01943827210526666</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3225219381673227</v>
+        <v>0.1677185863090448</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
@@ -2853,7 +2853,7 @@
         <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.4789401814735303</v>
+        <v>-0.02921224664006922</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -2862,16 +2862,16 @@
         <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.03621168993622688</v>
+        <v>-0.044980232090629</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.08392641192940255</v>
+        <v>0.02510271679474775</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.2574078785931929</v>
+        <v>-0.0350877866768199</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
@@ -2895,19 +2895,19 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.007314295111983563</v>
+        <v>-0.01322831978398022</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.115141886765301</v>
+        <v>-0.02528909145739172</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02331843279259169</v>
+        <v>0.03856050814221357</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
@@ -2922,19 +2922,19 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.07059959024571635</v>
+        <v>0.006138704455457823</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1781727930171658</v>
+        <v>0.1076282380751917</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1979086485276782</v>
+        <v>0.004227115961263941</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -2943,82 +2943,82 @@
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.00488085943665834</v>
+        <v>0.02357145382568274</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1038861614361757</v>
+        <v>-0.07523708764830746</v>
       </c>
       <c r="CF5" t="n">
         <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.03488674964409817</v>
+        <v>-0.01537249025626538</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.04206913905455223</v>
+        <v>0.002731485609388237</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.02145637450884574</v>
+        <v>-0.05992077892907351</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1089049939897628</v>
+        <v>0.008540087545378166</v>
       </c>
       <c r="CR5" t="n">
         <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.02036078594795076</v>
+        <v>0.01211837046721898</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1139003929461981</v>
+        <v>-0.0743894659469274</v>
       </c>
       <c r="CX5" t="n">
         <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.04026416177889461</v>
+        <v>-0.01905277530972968</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
@@ -3030,25 +3030,25 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.04493839130116217</v>
+        <v>-0.01032862272541124</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1875274110178539</v>
+        <v>-0.0905047687426246</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.05649414549275883</v>
+        <v>-0.01840018797698044</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
@@ -3057,76 +3057,76 @@
         <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.009301444905664357</v>
+        <v>0.01322425784602763</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.06128711365366424</v>
+        <v>-0.04704703997312582</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ5" t="n">
         <v>-0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02863705116881964</v>
+        <v>-0.0019067031359223</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.01869077340038714</v>
+        <v>0.04466877591831733</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.1076403665631798</v>
+        <v>0.06368389533471439</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
         <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.005961948635319173</v>
+        <v>-0.0006092070049153427</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.008485791879376207</v>
+        <v>0.01542237280318609</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.00363383302153466</v>
+        <v>-0.04841303506107855</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.07299780360063921</v>
+        <v>-0.04621483980957676</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3138,19 +3138,19 @@
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>-0.04290594969279698</v>
+        <v>0.008945668078527581</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1235556105872703</v>
+        <v>-0.03438401453670341</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.02123600500294088</v>
+        <v>-0.02946826486195636</v>
       </c>
       <c r="ET5" t="n">
         <v>-0</v>
@@ -3162,28 +3162,28 @@
         <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.02437214212471488</v>
+        <v>0.02178193480175416</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1214894522193733</v>
+        <v>-0.08342259494317582</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.08354860044338272</v>
+        <v>-0.02778808702216554</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,10 +3192,10 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.05602612254352083</v>
+        <v>-0.01267040066420021</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.06893779793840982</v>
+        <v>-0.03011305055648842</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
@@ -3204,10 +3204,10 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.08821924808190505</v>
+        <v>0.01413019978864495</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>-0.0423400122586951</v>
+        <v>0.09078210486905335</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.167986511602969</v>
+        <v>-0.03506036911755187</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
@@ -3231,63 +3231,63 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.1567237620936021</v>
+        <v>0.02436202188583718</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0.07575504651676304</v>
+        <v>0.04003953280565943</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.03286807119078958</v>
+        <v>-0.06088262371511832</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3812785321619613</v>
+        <v>0.4258068273121066</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1694143656723058</v>
+        <v>-0.2682492260885887</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.03435992364912276</v>
+        <v>-0.1212545884091745</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3302,19 +3302,19 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2362997506703447</v>
+        <v>0.3188334969567687</v>
       </c>
       <c r="L6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.149629274459679</v>
+        <v>-0.3162979185438552</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07328098644079953</v>
+        <v>-0.1556555105395471</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3326,55 +3326,55 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6" t="n">
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1224323408886262</v>
+        <v>0.1881731128333858</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0152360750155093</v>
+        <v>-0.0143765662696396</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05354811345283388</v>
+        <v>-0.01954852819151841</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.08642812043696359</v>
+        <v>0.03957579788825739</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.004316579954109074</v>
+        <v>-0.1275326433187847</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.05173629205317707</v>
+        <v>0.006742181104308301</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
@@ -3383,106 +3383,106 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.07617663721726015</v>
+        <v>0.2624684683640888</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.1118809801448217</v>
+        <v>-0.03875853166624855</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.009634301205878028</v>
+        <v>0.2325239700489916</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.725003781046978</v>
+        <v>0.7941864137901731</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.07949313641405288</v>
+        <v>-0.38097726728417</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.2362266119824392</v>
+        <v>-0.2276356407013806</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
         <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.01192337376001973</v>
+        <v>-0.03744533514177058</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.1035398301544021</v>
+        <v>-0.08165337869443487</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.2040649689931298</v>
+        <v>-0.07613832891108947</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.0219238008221353</v>
+        <v>-0.1030933221009471</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.1104229113063895</v>
+        <v>0.03285003661317266</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1055721498891214</v>
+        <v>0.1276694355989276</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3494,43 +3494,43 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.3075680429974299</v>
+        <v>0.4147462489113858</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.004430507961939481</v>
+        <v>-0.2008951766012147</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.05270172871232265</v>
+        <v>-0.04157325327667223</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.1336392634523985</v>
+        <v>-0.2800126473402147</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.07810258418312294</v>
+        <v>0.1848616485483467</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.05196415977310561</v>
+        <v>0.03489196459322088</v>
       </c>
       <c r="CI6" t="n">
         <v>-0</v>
@@ -3542,25 +3542,25 @@
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.01271251928142894</v>
+        <v>-0.1825563158059968</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.05012502961389123</v>
+        <v>0.07418834670944049</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1022658199349189</v>
+        <v>0.02221060132260582</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
@@ -3572,46 +3572,46 @@
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.1365923359310555</v>
+        <v>-0.3081968661826369</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.1058868204541644</v>
+        <v>0.1900899765979271</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.03806240924839802</v>
+        <v>0.06508862372717455</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0912339378222989</v>
+        <v>-0.3827098650037112</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1407611563149588</v>
+        <v>0.2512860024477412</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.1707066464000226</v>
+        <v>-0.14094239051368</v>
       </c>
       <c r="DJ6" t="n">
         <v>-0</v>
@@ -3620,7 +3620,7 @@
         <v>-0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
         <v>0</v>
@@ -3629,19 +3629,19 @@
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.1247043877790132</v>
+        <v>-0.08568384877899804</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.008983759066771539</v>
+        <v>0.1279197792134151</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.001979498232882827</v>
+        <v>-0.1246807686456167</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3656,43 +3656,43 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01504059979921221</v>
+        <v>0.1396511244671635</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.01293459343183118</v>
+        <v>0.1385010631217365</v>
       </c>
       <c r="EA6" t="n">
-        <v>5.107552007684209e-06</v>
+        <v>-0.0264120186266059</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
         <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.1413822234322081</v>
+        <v>-0.2190315953811195</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.07304958830774934</v>
+        <v>0.1391854845299578</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.08774517128380957</v>
+        <v>0.1041312090641571</v>
       </c>
       <c r="EK6" t="n">
         <v>-0</v>
@@ -3701,7 +3701,7 @@
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
@@ -3710,22 +3710,22 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.1089461349667605</v>
+        <v>-0.2673015050441845</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.1605727266975613</v>
+        <v>0.1322739285181757</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.1485361668141733</v>
+        <v>0.02581323663448055</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3737,46 +3737,46 @@
         <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1450547071949546</v>
+        <v>-0.3365068729433435</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.1059126758959564</v>
+        <v>0.218057357739164</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.06634169463828413</v>
+        <v>0.03248170461193498</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.05300743059966623</v>
+        <v>-0.1294942900895664</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>-0.0463865001702955</v>
+        <v>0.02940254565574877</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.008457960298254363</v>
+        <v>0.05929557762431423</v>
       </c>
       <c r="FL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,58 +3785,58 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.002079110807194588</v>
+        <v>-0.2464423707912246</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.1524123382181043</v>
+        <v>0.4624398838303261</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.2101171407231014</v>
+        <v>0.0712615499886062</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX6" t="n">
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01441411432483063</v>
+        <v>-0.2307602991155321</v>
       </c>
       <c r="GA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.06223652411080426</v>
+        <v>0.07700617526839124</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>-0</v>
@@ -3847,19 +3847,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1016973680807998</v>
+        <v>0.3573075571460395</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02721730641375935</v>
+        <v>0.01313359669363293</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.06073198400653956</v>
+        <v>-0.2713497393033093</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
@@ -3874,100 +3874,100 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06073383783868707</v>
+        <v>0.2896463815092561</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01605898527619951</v>
+        <v>-0.1044943126612154</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.05588491395296712</v>
+        <v>-0.2470122849172252</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02039360914881079</v>
+        <v>-0.09617615421793534</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.03497746726187886</v>
+        <v>-0.1206026059194846</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.003947647760359213</v>
+        <v>-0.1813482732128611</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0321880627448768</v>
+        <v>0.1994604339358315</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02038452056850628</v>
+        <v>-0.03231464020903877</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01791079696184005</v>
+        <v>0.1003310711751501</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01995243170688353</v>
+        <v>0.1192954464791952</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.007425677018413802</v>
+        <v>-0.01187385291278547</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.05318720939919193</v>
+        <v>-0.1676481557013557</v>
       </c>
       <c r="AQ7" t="n">
         <v>-0</v>
@@ -3979,37 +3979,37 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1364249820062339</v>
+        <v>0.6363611416480344</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.02561594167785896</v>
+        <v>-0.3382469062246604</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.1084717767853972</v>
+        <v>-0.4135842179110183</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.05090281864493962</v>
+        <v>0.1461486666725128</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,25 +4018,25 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.04348856040770584</v>
+        <v>0.06177567413973777</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.02887310770979394</v>
+        <v>-0.1668962816233436</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>-0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03837050666905963</v>
+        <v>0.08776413067374177</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
@@ -4045,25 +4045,25 @@
         <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.02087473450642496</v>
+        <v>0.1089159897376222</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01652660612439824</v>
+        <v>0.1514354327218691</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
         <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05541615162057174</v>
+        <v>0.1983609315508669</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -4072,10 +4072,10 @@
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.005188403251932413</v>
+        <v>-0.1187706707972885</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.03109424721886962</v>
+        <v>-0.3071351378346528</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4087,10 +4087,10 @@
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0332930937239632</v>
+        <v>-0.2518925167576225</v>
       </c>
       <c r="CF7" t="n">
         <v>0</v>
@@ -4099,64 +4099,64 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0007618372000925284</v>
+        <v>-0.04270497801459621</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.03559217992987387</v>
+        <v>0.2281274359976539</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.0112650977374101</v>
+        <v>-0.2129105789931451</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.0003512640359323723</v>
+        <v>0.05513614476627919</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.007631547386614847</v>
+        <v>0.1029180001501271</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.02834318802735003</v>
+        <v>-0.2363980750857851</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.001757657993266972</v>
+        <v>-0.02198700071558632</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0426212278974709</v>
+        <v>0.2035689402434175</v>
       </c>
       <c r="DB7" t="n">
         <v>-0</v>
@@ -4171,19 +4171,19 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.02091477879544664</v>
+        <v>-0.08472008553523271</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
         <v>-0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05524394331513081</v>
+        <v>-0.1089621874855058</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.01051896331294383</v>
+        <v>0.2502952319025813</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4192,52 +4192,52 @@
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.007067957412519478</v>
+        <v>-0.09488736134859584</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.03171364371925334</v>
+        <v>-0.03304899675958305</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.01811517453482528</v>
+        <v>0.07795227002249751</v>
       </c>
       <c r="DT7" t="n">
         <v>0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.026498696469635</v>
+        <v>0.1409394738819444</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.02095002976778464</v>
+        <v>0.02773059755098893</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.007214534531609083</v>
+        <v>0.08503048763109032</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4246,13 +4246,13 @@
         <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.02403849256547006</v>
+        <v>-0.1082544727003482</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
@@ -4261,10 +4261,10 @@
         <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.006802234213311103</v>
+        <v>-0.08351023557916065</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.02511395443923311</v>
+        <v>0.2394569984445362</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
@@ -4273,52 +4273,52 @@
         <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.02545338531931188</v>
+        <v>-0.148765089467003</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.004026820543187724</v>
+        <v>-0.1431874250371922</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0219950756683422</v>
+        <v>0.161224884334333</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02947346524537718</v>
+        <v>-0.2455212200716254</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.003383881091335054</v>
+        <v>-0.08275806113074118</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.04046164040873135</v>
+        <v>0.2116348240588787</v>
       </c>
       <c r="FD7" t="n">
         <v>0</v>
@@ -4327,105 +4327,105 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01735323767017074</v>
+        <v>-0.1416292946265496</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.03435179325948972</v>
+        <v>0.07465036978700569</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.03416510204113753</v>
+        <v>0.2351645648902757</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.03166578801400931</v>
+        <v>-0.01550532076599426</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.002003388717093079</v>
+        <v>0.07199198979355491</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.001582434494179177</v>
+        <v>0.02537335584190496</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02587202774703778</v>
+        <v>-0.08175087141127023</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.02095374041883059</v>
+        <v>0.1832444236926215</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.335864435822894</v>
+        <v>0.4227276677460683</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08016060459805723</v>
+        <v>-0.1474750988534863</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.05121955894369766</v>
+        <v>-0.1123872014151285</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -4437,22 +4437,22 @@
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1853480568233725</v>
+        <v>0.3039627040633084</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.05959278085935254</v>
+        <v>-0.1753310415213769</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.05813057493241085</v>
+        <v>-0.1251563027386486</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4461,28 +4461,28 @@
         <v>-0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.116226402918347</v>
+        <v>0.1484631442795445</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.02085383117101888</v>
+        <v>0.02903290772300346</v>
       </c>
       <c r="W8" t="n">
-        <v>0.005037482487882123</v>
+        <v>-0.07311793207757468</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
@@ -4494,100 +4494,100 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.07205185309584539</v>
+        <v>0.0320656459671629</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.02817880894289172</v>
+        <v>-0.107607844226851</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.05086932276474301</v>
+        <v>-0.07265288789568451</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.05473956135150947</v>
+        <v>0.2279389396005553</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.04868088500907264</v>
+        <v>0.01411153172632536</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.06204312298095832</v>
+        <v>0.08822537744601724</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
         <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.5084868573757843</v>
+        <v>0.5512380186703149</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.08087755984372291</v>
+        <v>-0.2434639507794873</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1205014758183244</v>
+        <v>-0.2836639542974789</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.05525028835543956</v>
+        <v>0.02262707731865215</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.05936113984232721</v>
+        <v>-0.1149221274176021</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1680039165821929</v>
+        <v>-0.03606205601051717</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
@@ -4596,7 +4596,7 @@
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
@@ -4605,22 +4605,22 @@
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.08387782580819737</v>
+        <v>-0.03507681932884853</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.07854955967003864</v>
+        <v>0.06743675542839313</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.1146585388256861</v>
+        <v>0.1473309304110667</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>-0</v>
@@ -4632,25 +4632,25 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1992722403346225</v>
+        <v>0.3341067377813778</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0.01558622307794913</v>
+        <v>-0.1393081191218309</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.01788575060547101</v>
+        <v>-0.05956011382238192</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
         <v>0</v>
@@ -4659,16 +4659,16 @@
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.103010423760989</v>
+        <v>-0.2031066798806949</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.04001874773938021</v>
+        <v>0.1875576285643476</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.02184235538362342</v>
+        <v>0.02366310207598117</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
@@ -4680,25 +4680,25 @@
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.0139576569576266</v>
+        <v>-0.1151378725290555</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.01550528116943679</v>
+        <v>0.0214231370151194</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.06391440454239455</v>
+        <v>0.002977387616819688</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
@@ -4707,22 +4707,22 @@
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.09667634785797502</v>
+        <v>-0.2156022615966065</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.06750691774020992</v>
+        <v>0.1912667394297853</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.02123058445591195</v>
+        <v>0.03486548028522027</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
@@ -4731,31 +4731,31 @@
         <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.07362571629346666</v>
+        <v>-0.1800275878247657</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.1566618167261187</v>
+        <v>0.1411750471273218</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.02124462773582181</v>
+        <v>-0.05730231560381218</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
@@ -4767,22 +4767,22 @@
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.07064607706485088</v>
+        <v>-0.140719368976003</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.05780323590420577</v>
+        <v>0.1115498155959457</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.02606106327016965</v>
+        <v>-0.1054306664540876</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU8" t="n">
         <v>-0</v>
@@ -4794,52 +4794,52 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.04015258383659293</v>
+        <v>0.07357557565463856</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.009522711832586111</v>
+        <v>0.1377606743065603</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.028116885288178</v>
+        <v>-0.07316602443784441</v>
       </c>
       <c r="EB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.07997262301489994</v>
+        <v>-0.1283010579161512</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>-0.1047623354372142</v>
+        <v>-0.2424627594375186</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.06892877359577818</v>
+        <v>0.03547206843076335</v>
       </c>
       <c r="EK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
@@ -4848,22 +4848,22 @@
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.08345729212634043</v>
+        <v>-0.1759634839856693</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.09563754520127309</v>
+        <v>0.1046026283135694</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.05848246191486688</v>
+        <v>-0.0202986760893317</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4872,49 +4872,49 @@
         <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.09449573124455923</v>
+        <v>-0.2387462203818386</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0651302716726615</v>
+        <v>0.2005273170583805</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.02708025500254186</v>
+        <v>0.01377248939356135</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.01476032502771375</v>
+        <v>-0.04755338770198451</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.04081271650757715</v>
+        <v>-0.08519666231763251</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.01967628406298906</v>
+        <v>0.06999470299566835</v>
       </c>
       <c r="FL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM8" t="n">
         <v>-0</v>
@@ -4923,22 +4923,22 @@
         <v>-0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.003516346235678848</v>
+        <v>-0.1157437073122451</v>
       </c>
       <c r="FR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.01743604491365759</v>
+        <v>0.3287064823977873</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.06745956634249246</v>
+        <v>0.122058303849627</v>
       </c>
       <c r="FU8" t="n">
         <v>-0</v>
@@ -4947,34 +4947,34 @@
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.0267080321621981</v>
+        <v>-0.1696109317823135</v>
       </c>
       <c r="GA8" t="n">
         <v>-0</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.03953775257895663</v>
+        <v>0.07361740880437492</v>
       </c>
       <c r="GC8" t="n">
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>-0</v>
@@ -4982,133 +4982,133 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.05788608340990446</v>
+        <v>-0.1618971815160878</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1815021971562636</v>
+        <v>0.1321362527347062</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1336017109340511</v>
+        <v>-0.1171657894688389</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.00919073913198014</v>
+        <v>-0.00416399259707855</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.00683516682111405</v>
+        <v>-0.1219032353240169</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08816634960115566</v>
+        <v>0.06392545524647829</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04693099404190745</v>
+        <v>-0.1513918089655863</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.005611272276058499</v>
+        <v>-0.0003786602227076933</v>
       </c>
       <c r="Q9" t="n">
         <v>-0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.05661622823773504</v>
+        <v>0.007877421194147265</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.112264633590098</v>
+        <v>-0.03934585212564388</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03519637834539967</v>
+        <v>-0.1073019235333594</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.0672630056554174</v>
+        <v>0.02674947197642868</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.03686680807125396</v>
+        <v>0.1320147805704526</v>
       </c>
       <c r="AC9" t="n">
         <v>-0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.06389807965042056</v>
+        <v>-0.09660248959987888</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.04312317417994364</v>
+        <v>-0.2025344976502201</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.01101328872300908</v>
+        <v>0.04660335335221484</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0238337187835331</v>
+        <v>0.006659530994573988</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.04605721957157247</v>
+        <v>-0.06096954219915855</v>
       </c>
       <c r="AN9" t="n">
         <v>-0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.01302150064782477</v>
+        <v>-0.01714286322299703</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.002204374580670745</v>
+        <v>0.03743088589066678</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -5117,106 +5117,106 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0.06549740249086611</v>
+        <v>-0.150358753397611</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2754885579625315</v>
+        <v>0.09573283885381537</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.4158856483966702</v>
+        <v>-0.2391137129027802</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.05671530121922216</v>
+        <v>0.01073198211945634</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0.1060481688863743</v>
+        <v>-0.04087246489940742</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.01124037340841806</v>
+        <v>-0.01599986601833573</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.01281235424276057</v>
+        <v>0.08047753909784339</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0.009063283191276876</v>
+        <v>-0.09230744677316349</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0.01559566388479444</v>
+        <v>0.07980193767187051</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.1320579678140044</v>
+        <v>0.04543768167901033</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0369357885327022</v>
+        <v>0.05503561710345992</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0281257453759757</v>
+        <v>0.01949577267055768</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>-0.01687800023224372</v>
+        <v>-0.05503797247365185</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.06469577188750748</v>
+        <v>0.07431807532904915</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.1833206410782433</v>
+        <v>-0.1299084203057475</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>-0.01498568711955931</v>
+        <v>0.03175535903420831</v>
       </c>
       <c r="CB9" t="n">
         <v>-0</v>
@@ -5225,187 +5225,187 @@
         <v>-0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.04554032894325386</v>
+        <v>0.06644648900130935</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF9" t="n">
-        <v>-0.06037963099038481</v>
+        <v>0.004935736430901239</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.04839841208914324</v>
+        <v>0.09637940226011424</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.007528866573239542</v>
+        <v>0.008880078461872398</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.02685802018789925</v>
+        <v>-0.05521239117110544</v>
       </c>
       <c r="CN9" t="n">
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>-0.007976657480916144</v>
+        <v>0.03469734621976062</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.08884646594310627</v>
+        <v>-0.0209008830922024</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0.003589570875640458</v>
+        <v>0.01552334851335554</v>
       </c>
       <c r="CT9" t="n">
         <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.02639966255405387</v>
+        <v>0.07105307408404252</v>
       </c>
       <c r="CW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0.05285503876585679</v>
+        <v>-0.0411559766937202</v>
       </c>
       <c r="CY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.01877722033536568</v>
+        <v>0.05169016568425698</v>
       </c>
       <c r="DA9" t="n">
         <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.01503495287978257</v>
+        <v>0.02813806954016557</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.04726571367101567</v>
+        <v>-0.03404718099343913</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0.08475049849379315</v>
+        <v>-0.04061977315554532</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03612665746017211</v>
+        <v>0.1976304909475815</v>
       </c>
       <c r="DJ9" t="n">
         <v>0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.02497663091917523</v>
+        <v>-0.04174628872609548</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
         <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.07232422805341704</v>
+        <v>-0.1052250302359927</v>
       </c>
       <c r="DO9" t="n">
         <v>-0</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0168527652958397</v>
+        <v>0.03167844732075911</v>
       </c>
       <c r="DQ9" t="n">
         <v>-0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.01115208614911097</v>
+        <v>-0.190060378707209</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.05495590415830272</v>
+        <v>0.005330910425235052</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0.02036551922747463</v>
+        <v>0.02504328043491821</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY9" t="n">
-        <v>-0.01219392307425016</v>
+        <v>0.129174817993013</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.09692234363862101</v>
+        <v>-0.2141500289433251</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>-0.01349757635573772</v>
+        <v>-0.01572547185877738</v>
       </c>
       <c r="ED9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.008193221626349705</v>
+        <v>0.06470209199655758</v>
       </c>
       <c r="EG9" t="n">
         <v>0</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0.1318858172905738</v>
+        <v>0.004102590975319231</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.02728949147198647</v>
+        <v>0.05858967857591974</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0.01192332051362069</v>
+        <v>0.09862484923601299</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5414,79 +5414,79 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.02658603161311449</v>
+        <v>0.0783375275576173</v>
       </c>
       <c r="EP9" t="n">
         <v>0</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0.03819333977205885</v>
+        <v>0.07056924364169118</v>
       </c>
       <c r="ER9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.1151233744093987</v>
+        <v>0.02405219280942658</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0.04176888885913603</v>
+        <v>0.05695230448603427</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0261471974625578</v>
+        <v>0.07466601916532593</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0.05306044007526813</v>
+        <v>-0.04181345869424173</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.03673145880035578</v>
+        <v>0.08345711046348335</v>
       </c>
       <c r="FC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.008353270826779991</v>
+        <v>0.003661632733546887</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.01631275198388751</v>
+        <v>0.3066040290988293</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0.02710202071889388</v>
+        <v>-0.004369665642364254</v>
       </c>
       <c r="FJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.007366490656097324</v>
+        <v>0.06896092326506209</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0.03901782492044522</v>
+        <v>0.05131999949787641</v>
       </c>
       <c r="FN9" t="n">
         <v>0</v>
@@ -5495,25 +5495,25 @@
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.05608232799000169</v>
+        <v>0.2850318939852664</v>
       </c>
       <c r="FQ9" t="n">
         <v>0</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.05783838722324708</v>
+        <v>-0.184435763320063</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.07726609341720039</v>
+        <v>0.1406485803717429</v>
       </c>
       <c r="FU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0.03642265489569341</v>
+        <v>0.03412662351415484</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
@@ -5522,13 +5522,13 @@
         <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0.02411659739193115</v>
+        <v>0.1407654355472188</v>
       </c>
       <c r="FZ9" t="n">
         <v>-0</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.05047075918228985</v>
+        <v>-0.01019812508059388</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
@@ -5537,13 +5537,13 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
-        <v>-0.03691696161622758</v>
+        <v>0.09024869297415396</v>
       </c>
       <c r="GF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5551,37 +5551,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1151204899765378</v>
+        <v>0.5295810597361483</v>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.02092172408318963</v>
+        <v>0.02797799201724051</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.06676800383521174</v>
+        <v>-0.3711936267909695</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07797338020756629</v>
+        <v>0.4841907046156198</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,70 +5590,70 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.01157154544805399</v>
+        <v>-0.1193246565032685</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.04210387873562071</v>
+        <v>-0.2422645370936673</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01431905265736977</v>
+        <v>0.02345603971083835</v>
       </c>
       <c r="U10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01952283171944304</v>
+        <v>-0.09776265841203681</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.01310975601141354</v>
+        <v>-0.1354044398239504</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.02597342526644785</v>
+        <v>0.161677495734747</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01854928381396232</v>
+        <v>-0.1201325708375567</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01316618248598362</v>
+        <v>0.01971103066028377</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0</v>
@@ -5662,22 +5662,22 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01549707262205767</v>
+        <v>0.2000258865803243</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.004764509572918219</v>
+        <v>0.0152218754580064</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.04305993914684136</v>
+        <v>-0.2101439024108893</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,55 +5686,55 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1151233512809443</v>
+        <v>0.8901261465306469</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.00245648877360229</v>
+        <v>-0.3305583838836109</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.07163683650538605</v>
+        <v>-0.3379277712384645</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.06049436374050307</v>
+        <v>0.04530977936975148</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.04144789175368151</v>
+        <v>-0.03143954969582993</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.03445932173573283</v>
+        <v>-0.2471704429836992</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>-0</v>
@@ -5743,34 +5743,34 @@
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0387589917503399</v>
+        <v>0.1344202384065315</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.01746545324090725</v>
+        <v>0.1334563790916975</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.009276895659341181</v>
+        <v>0.1155168921537123</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.0424771899982269</v>
+        <v>0.3454753507818357</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -5779,13 +5779,13 @@
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.001492480944659899</v>
+        <v>-0.09970726476920926</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.02674183544278151</v>
+        <v>-0.2805360795847132</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
         <v>-0</v>
@@ -5794,25 +5794,25 @@
         <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.02913988030080759</v>
+        <v>-0.2824106643663675</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0006505439942389189</v>
+        <v>-0.01753712742025257</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02331834258012232</v>
+        <v>0.222915067314197</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
@@ -5824,22 +5824,22 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.007632874078275126</v>
+        <v>-0.2444356609078919</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.0008434791569870069</v>
+        <v>0.1119721418810527</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.009972759366994937</v>
+        <v>0.1127542532037355</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
         <v>0</v>
@@ -5848,22 +5848,22 @@
         <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02484694950920264</v>
+        <v>-0.2660854518821831</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.001322080844895328</v>
+        <v>-0.02693051973011957</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.02681291255239064</v>
+        <v>0.2117271126396804</v>
       </c>
       <c r="DB10" t="n">
         <v>-0</v>
@@ -5878,19 +5878,19 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.006581800404819493</v>
+        <v>-0.05350521093232551</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
         <v>-0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01357526554862264</v>
+        <v>-0.06911525364513127</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.02265153697382258</v>
+        <v>0.1066397288453582</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
@@ -5899,25 +5899,25 @@
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.007422358183497637</v>
+        <v>-0.09595178438616273</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.03500675228092703</v>
+        <v>-0.07901306945543263</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.00128405706989788</v>
+        <v>0.1272854307861203</v>
       </c>
       <c r="DT10" t="n">
         <v>0</v>
@@ -5932,46 +5932,46 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.02878916559549991</v>
+        <v>0.09568008348762752</v>
       </c>
       <c r="DY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ10" t="n">
         <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.02620787412414134</v>
+        <v>0.03291173619085818</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.00307274141859797</v>
+        <v>0.005157757164868783</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02236687988693072</v>
+        <v>-0.1021944892650295</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.004092460561938338</v>
+        <v>-0.09756889349868453</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.01017318114907781</v>
+        <v>0.1760943342745084</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
@@ -5980,67 +5980,67 @@
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.02219957872817279</v>
+        <v>-0.1952954724624374</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.01914981359279312</v>
+        <v>-0.08355159145692086</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.02250390725052903</v>
+        <v>0.111064775616561</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
         <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.02728558989224517</v>
+        <v>-0.2878933361986667</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.00438637020960511</v>
+        <v>-0.06571656179606625</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.02818129825561505</v>
+        <v>0.2012658147122917</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.008747769962244224</v>
+        <v>-0.2275849936747927</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
@@ -6049,13 +6049,13 @@
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03050229433870029</v>
+        <v>0.1104129980476986</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.03069885977770058</v>
+        <v>0.2127200358143988</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
         <v>0</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.01310128631844835</v>
+        <v>-0.08522201515388848</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,46 +6076,46 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.004150505233080067</v>
+        <v>0.05758354185416622</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.000897076828779119</v>
+        <v>-0.008363896172078425</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.02374646192893499</v>
+        <v>-0.1173616369689741</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.02541237171488437</v>
+        <v>0.0914295913115485</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,43 +6123,43 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4983968840139405</v>
+        <v>0.3604057409234553</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1960818227080932</v>
+        <v>-0.2785397013317374</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1340491263732326</v>
+        <v>0.08797310921357238</v>
       </c>
       <c r="F11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3933200085796679</v>
+        <v>0.3600538255655048</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1239171608252099</v>
+        <v>-0.2163782927131096</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1356498282216958</v>
+        <v>0.04658681691272817</v>
       </c>
       <c r="O11" t="n">
         <v>-0</v>
@@ -6177,19 +6177,19 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1211826115375206</v>
+        <v>0.06619316939376525</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01095062510312352</v>
+        <v>-0.03274277515602217</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1292355755413719</v>
+        <v>-0.1303828939563358</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
@@ -6198,28 +6198,28 @@
         <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2145290972688035</v>
+        <v>0.1383620915310121</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.01043596495082893</v>
+        <v>-0.08976088091137779</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.04302476753102772</v>
+        <v>-0.193806823978149</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
@@ -6228,46 +6228,46 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.01027778191419253</v>
+        <v>0.2530478168768155</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.08596980347090974</v>
+        <v>-0.1068056640545205</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.12243702146784</v>
+        <v>0.04906026014784034</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.6058274128564402</v>
+        <v>0.3924972068635012</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.06868592794873193</v>
+        <v>-0.1181860844073677</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.04564711082150145</v>
+        <v>-0.146363921866385</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
@@ -6285,16 +6285,16 @@
         <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.1483809576332202</v>
+        <v>-0.005859445698918653</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.07806925391885007</v>
+        <v>-0.09566695328635751</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.08846264585331852</v>
+        <v>-0.0700505154715132</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6312,16 +6312,16 @@
         <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1333130321339134</v>
+        <v>0.01804509057280179</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.05642358230947121</v>
+        <v>0.08592077658506862</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.2431474176461969</v>
+        <v>0.05588453889883547</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
@@ -6339,49 +6339,49 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2655376010211759</v>
+        <v>0.2384371486717977</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0.01386405303996211</v>
+        <v>-0.1156002323066782</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.09254182175893665</v>
+        <v>0.008843427423850764</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
         <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1281870918071553</v>
+        <v>-0.2016494767960739</v>
       </c>
       <c r="CF11" t="n">
         <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.02533457435841729</v>
+        <v>0.2200365598884417</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.02706250577385388</v>
+        <v>-0.04763757585924158</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,25 +6393,25 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.09953865882393335</v>
+        <v>-0.117654040865157</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.1079579257310274</v>
+        <v>0.4266414419752668</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1424554843724411</v>
+        <v>0.06810123646874298</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
         <v>-0</v>
@@ -6420,25 +6420,25 @@
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1141336217733712</v>
+        <v>-0.1818370440048685</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.04208438202404405</v>
+        <v>0.2087367797153409</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01777326761555184</v>
+        <v>-0.04210934432853009</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,43 +6447,43 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.01228429709374339</v>
+        <v>0.05441748795021601</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.1776468562669744</v>
+        <v>0.03784836446039943</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01381009069896385</v>
+        <v>-0.07890500375696384</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.130575598739882</v>
+        <v>-0.1936723748843055</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0.1140455576315816</v>
+        <v>0.1841398824180874</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.1055108489354035</v>
+        <v>0.01730871904659783</v>
       </c>
       <c r="DS11" t="n">
         <v>-0</v>
@@ -6492,79 +6492,79 @@
         <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.176030720148956</v>
+        <v>-0.1495519682231477</v>
       </c>
       <c r="DY11" t="n">
         <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.04752365240029822</v>
+        <v>-0.1413070172539429</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.07870372961090372</v>
+        <v>-0.1222785944010389</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.1207310531500281</v>
+        <v>-0.02977690860972917</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.1173638690234988</v>
+        <v>0.1404211739330517</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.1892873251444971</v>
+        <v>0.01038686973650749</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1205206906531203</v>
+        <v>-0.2036384157230767</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0339314158934968</v>
+        <v>0.1146674010256109</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.09209771468745467</v>
+        <v>0.008906699316509899</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6573,25 +6573,25 @@
         <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1125613003437676</v>
+        <v>-0.2123555261738136</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.04872843462208998</v>
+        <v>0.2370391852821808</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.04773965018940341</v>
+        <v>-0.05372479426343821</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
@@ -6600,25 +6600,25 @@
         <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.1960593038356874</v>
+        <v>-0.1204558697832805</v>
       </c>
       <c r="FI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.05314042000316321</v>
+        <v>0.06779881312093826</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.0954602950584733</v>
+        <v>-0.3317584458623004</v>
       </c>
       <c r="FL11" t="n">
         <v>-0</v>
@@ -6627,28 +6627,28 @@
         <v>-0</v>
       </c>
       <c r="FN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.02940615222200384</v>
+        <v>-0.04348059761236453</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>-0.03638503545686785</v>
+        <v>-0.03279345715858498</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.09063597326374805</v>
+        <v>0.04415975010635115</v>
       </c>
       <c r="FU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV11" t="n">
         <v>0</v>
@@ -6663,60 +6663,60 @@
         <v>-0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.08553080704328381</v>
+        <v>-0.07430755908994677</v>
       </c>
       <c r="GA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.06801081502832355</v>
+        <v>0.2782573097228013</v>
       </c>
       <c r="GC11" t="n">
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.2070634505277382</v>
+        <v>0.1211407281720874</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C12" t="n">
         <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1527891103966427</v>
+        <v>-0.2259700204880312</v>
       </c>
       <c r="E12" t="n">
-        <v>0.139728663288919</v>
+        <v>0.06119051836944039</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1917258400045113</v>
+        <v>0.07345480424804739</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -6725,25 +6725,25 @@
         <v>-0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.04985037874858319</v>
+        <v>-0.2489647685771842</v>
       </c>
       <c r="N12" t="n">
-        <v>0.07265805899522786</v>
+        <v>0.01180178171278852</v>
       </c>
       <c r="O12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.03951392609810863</v>
+        <v>-0.02075182520075773</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -6752,91 +6752,91 @@
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1158493505250817</v>
+        <v>-0.04601566016430563</v>
       </c>
       <c r="W12" t="n">
-        <v>0.07559995758532403</v>
+        <v>-0.05899608221467662</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>-0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.07514302565019154</v>
+        <v>0.03836159916892905</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.05468898661808234</v>
+        <v>0.05814216846345032</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.03315903206327819</v>
+        <v>0.1747435259538449</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.03081981300858528</v>
+        <v>0.03270711358065359</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.02821140374572752</v>
+        <v>-0.1404576521224002</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.06527354417435588</v>
+        <v>0.04789065645693523</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>-0</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.1507135222550541</v>
+        <v>-0.06397084095699487</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.06687335919845093</v>
+        <v>-0.3505869526169145</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.2616230709455466</v>
+        <v>-0.02230971754025507</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6851,7 +6851,7 @@
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.2190484409978439</v>
+        <v>0.1661245603880065</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
@@ -6860,37 +6860,37 @@
         <v>-0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.01422336449566378</v>
+        <v>0.2068981614639333</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.05924868341714198</v>
+        <v>0.1684847092327525</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.08814029639012623</v>
+        <v>-0.003613179619675863</v>
       </c>
       <c r="BM12" t="n">
         <v>0</v>
       </c>
       <c r="BN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.03412363422752315</v>
+        <v>0.01389766238075032</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1706622831733927</v>
+        <v>-0.1089563399075943</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
@@ -6899,25 +6899,25 @@
         <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0465102087152437</v>
+        <v>-0.04801164201136012</v>
       </c>
       <c r="BV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW12" t="n">
         <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.007585108612994046</v>
+        <v>-0.1967194947099738</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.110756428040185</v>
+        <v>-0.03917618133221584</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -6926,13 +6926,13 @@
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>-0.03724474927715508</v>
+        <v>-0.05510357444304977</v>
       </c>
       <c r="CE12" t="n">
         <v>0</v>
@@ -6941,16 +6941,16 @@
         <v>0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.02055046533162123</v>
+        <v>0.1077389389097189</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.0429480442387252</v>
+        <v>-0.02004315818429219</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6959,61 +6959,61 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>-0.05572466906644654</v>
+        <v>-0.0008004771742731702</v>
       </c>
       <c r="CN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.1332427231054665</v>
+        <v>0.1108377789218846</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1162277573287646</v>
+        <v>-0.04935645159439225</v>
       </c>
       <c r="CR12" t="n">
         <v>0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0.01667374347957047</v>
+        <v>-0.04688053165691792</v>
       </c>
       <c r="CW12" t="n">
         <v>-0</v>
       </c>
       <c r="CX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.006332038206917859</v>
+        <v>0.1095484196360995</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.03487417398405242</v>
+        <v>-0.001650573257281331</v>
       </c>
       <c r="DA12" t="n">
         <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0.02163093039542517</v>
+        <v>-0.00356116194881815</v>
       </c>
       <c r="DF12" t="n">
         <v>-0</v>
@@ -7022,10 +7022,10 @@
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.07475444571538935</v>
+        <v>0.08129640828805447</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.03584592152099914</v>
+        <v>-0.01676680481950708</v>
       </c>
       <c r="DJ12" t="n">
         <v>0</v>
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0.0502686641409219</v>
+        <v>-0.06579225939158799</v>
       </c>
       <c r="DO12" t="n">
         <v>-0</v>
@@ -7049,70 +7049,70 @@
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0689678159436011</v>
+        <v>0.01358216993179534</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.1076274657611254</v>
+        <v>0.01236702613106507</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0.07151857677275862</v>
+        <v>0.01347315508193833</v>
       </c>
       <c r="DX12" t="n">
         <v>-0</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.02347601385324561</v>
+        <v>0.01324501646482771</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.08979990174464668</v>
+        <v>0.02690201716855667</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0.03874323153515925</v>
+        <v>-0.08607162868138776</v>
       </c>
       <c r="EG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.02977845107568349</v>
+        <v>0.09918299477684325</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.01780462056955368</v>
+        <v>0.02006589166306759</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>0</v>
@@ -7121,22 +7121,22 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.01243484029829679</v>
+        <v>0.0279013410814376</v>
       </c>
       <c r="EP12" t="n">
         <v>0</v>
       </c>
       <c r="EQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.03368536203129598</v>
+        <v>0.1194958974062769</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.01847656782168937</v>
+        <v>0.01951838139490126</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
@@ -7148,34 +7148,34 @@
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>-0.02151086311395828</v>
+        <v>-0.05383611330695823</v>
       </c>
       <c r="EY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0.01032136593724652</v>
+        <v>0.1409603175517452</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.04605219388245954</v>
+        <v>-0.01163953021819537</v>
       </c>
       <c r="FC12" t="n">
         <v>0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0.0426524212475698</v>
+        <v>0.01690408517940004</v>
       </c>
       <c r="FH12" t="n">
         <v>0</v>
@@ -7184,10 +7184,10 @@
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.02823741710139682</v>
+        <v>0.09958957096224487</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.1862454436008055</v>
+        <v>0.1305197848836541</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
@@ -7196,13 +7196,13 @@
         <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
         <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.007815398110875709</v>
+        <v>-0.006106269398164259</v>
       </c>
       <c r="FQ12" t="n">
         <v>-0</v>
@@ -7211,34 +7211,34 @@
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.0285089755736265</v>
+        <v>0.2291507346583974</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.07697554240654686</v>
+        <v>0.07460672935131413</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.03651876679948103</v>
+        <v>0.01987395830541937</v>
       </c>
       <c r="FZ12" t="n">
         <v>0</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.0508204063516501</v>
+        <v>0.1903930481415776</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
@@ -8399,22 +8399,22 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.559524000778469</v>
+        <v>0.3129544858893787</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2330714662812555</v>
+        <v>-0.1522348581145022</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.02770239934542904</v>
+        <v>-0.06054775312193345</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3230855615148865</v>
+        <v>0.2967024060103832</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2397277187806909</v>
+        <v>-0.2015315886581548</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.02953011226699564</v>
+        <v>-0.1093389791354686</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8453,76 +8453,76 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.120066479444405</v>
+        <v>0.03975427820473097</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.001989388732499831</v>
+        <v>-0.05146555047132426</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1981399025553424</v>
+        <v>-0.07338353732334585</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.09296925325541129</v>
+        <v>-0.0722500547200715</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.05401021876134467</v>
+        <v>-0.09776391800451797</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.06264986771571722</v>
+        <v>-0.06291256572592854</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.01235659805607243</v>
+        <v>0.0969240921655647</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.06100369606455219</v>
+        <v>-0.09965126744366093</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0002119291363684451</v>
+        <v>0.05204442113764492</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8534,25 +8534,25 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.5098456828529349</v>
+        <v>0.2657099499193543</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.09552904747648819</v>
+        <v>-0.0600998929872754</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1819136161770179</v>
+        <v>-0.1597602810296587</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>-0</v>
@@ -8561,25 +8561,25 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.08121509447588829</v>
+        <v>-0.006391949691019367</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.2667270040379431</v>
+        <v>-0.02478779232793465</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.186434618143963</v>
+        <v>-0.04449380173021578</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,70 +8588,70 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.1251908454217623</v>
+        <v>-0.01179273096250095</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0.003148522337728738</v>
+        <v>0.05499549609912618</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.2043354629318599</v>
+        <v>0.04739752902133432</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1528064659880441</v>
+        <v>0.1456380305265589</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.03774634467414721</v>
+        <v>-0.09647464657329732</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.1017985922537798</v>
+        <v>-0.02685765196501011</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1252460441192026</v>
+        <v>-0.1065988158494016</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.005043077300149587</v>
+        <v>0.09202045237825149</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.02220350025576284</v>
+        <v>0.01385107251609353</v>
       </c>
       <c r="CI15" t="n">
         <v>-0</v>
@@ -8663,25 +8663,25 @@
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.001641613671571868</v>
+        <v>-0.06153989477416343</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.234997905177404</v>
+        <v>0.1632184907034185</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.08469055862311795</v>
+        <v>0.03710302634963917</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
@@ -8696,43 +8696,43 @@
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.0891056202446842</v>
+        <v>-0.106157982701392</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.03755195343861334</v>
+        <v>0.09937784504360463</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.03639352869303281</v>
+        <v>0.02520446763208374</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.02845429717720982</v>
+        <v>-0.04766276393289846</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.08827535161278906</v>
+        <v>0.02720481866004532</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.04361921855614237</v>
+        <v>-0.08619502799551179</v>
       </c>
       <c r="DJ15" t="n">
         <v>-0</v>
@@ -8747,28 +8747,28 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.08181816000405309</v>
+        <v>-0.05702110941019668</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.02359114695772073</v>
+        <v>-0.0267844321647682</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.04949029273662999</v>
+        <v>-0.02575022804124076</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
@@ -8777,16 +8777,16 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.05132575569395859</v>
+        <v>-0.002414347075065819</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.0520147183943462</v>
+        <v>0.07028128159804879</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.08288540225719272</v>
+        <v>-0.0007819913975252653</v>
       </c>
       <c r="EB15" t="n">
         <v>-0</v>
@@ -8795,52 +8795,52 @@
         <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.1034471576652698</v>
+        <v>-0.08158634206860667</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0.02708120228071764</v>
+        <v>0.06665113387132716</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.08740387655414349</v>
+        <v>0.06338811704014582</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.009553618274564005</v>
+        <v>-0.04153981445491703</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.01987120470674911</v>
+        <v>0.06431711266781782</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.01159875883617959</v>
+        <v>-0.004923844471995725</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
@@ -8858,25 +8858,25 @@
         <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.0855048522954759</v>
+        <v>-0.1121471316519863</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.02447884065062331</v>
+        <v>0.1187886044090597</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.003702749208864165</v>
+        <v>0.006023998426831777</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>0</v>
@@ -8885,16 +8885,16 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.01479937446324157</v>
+        <v>0.1073044837231265</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.008459869775285591</v>
+        <v>0.07366274000973731</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.02279557559513727</v>
+        <v>0.01470913974689237</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8906,28 +8906,28 @@
         <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.04621183659143154</v>
+        <v>0.04378216511573787</v>
       </c>
       <c r="FR15" t="n">
         <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.03337502380121125</v>
+        <v>0.1042751487820166</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.05881057984368338</v>
+        <v>-0.01968128517293833</v>
       </c>
       <c r="FU15" t="n">
         <v>-0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
         <v>-0</v>
@@ -8936,25 +8936,25 @@
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.07406946616481051</v>
+        <v>-0.06692114248400161</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.1428375052823531</v>
+        <v>0.03462950064163612</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
         <v>0</v>
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1508827158852239</v>
+        <v>0.2402173319976812</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,25 +8977,25 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05540472024496717</v>
+        <v>0.001111593287612051</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.08895143080684446</v>
+        <v>-0.1102826193400708</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1136448567996548</v>
+        <v>0.2448689779845244</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,67 +9004,67 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.03699303312441549</v>
+        <v>-0.06109390333548194</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.06991022176452612</v>
+        <v>-0.118317213545678</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01178140136480864</v>
+        <v>0.05990102900099524</v>
       </c>
       <c r="U16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.008926459609585118</v>
+        <v>-0.08081952019625631</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01436220799389488</v>
+        <v>-0.005159166439724939</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.01322699201789526</v>
+        <v>-0.03180857135565417</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01653185008956016</v>
+        <v>-0.146242924045017</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.004366665881559117</v>
+        <v>0.02679393606997117</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
@@ -9076,22 +9076,22 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.008973212011039849</v>
+        <v>0.02234935147164802</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01569315526480149</v>
+        <v>-0.03136037861295423</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.01367214951701976</v>
+        <v>0.003433125970518289</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9100,10 +9100,10 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1153938711451974</v>
+        <v>0.2022584681956612</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
@@ -9112,25 +9112,25 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.01787878461818319</v>
+        <v>-0.1793802425088967</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.02147783924078349</v>
+        <v>-0.0778709800041215</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
         <v>-0</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.04234387283958466</v>
+        <v>0.01781549608877071</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,13 +9139,13 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.05423539485419909</v>
+        <v>0.002091080394419572</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.07088993894401294</v>
+        <v>-0.06049531310338922</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
         <v>-0</v>
@@ -9154,37 +9154,37 @@
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0439984694098617</v>
+        <v>0.0166954775618248</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.02614911999761512</v>
+        <v>0.06494370061543805</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.02462848970999234</v>
+        <v>-0.003852677009463982</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.04266072859301578</v>
+        <v>0.08700227029725847</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -9193,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.008102824211839761</v>
+        <v>-0.03004847284499008</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.003687665916994841</v>
+        <v>-0.0596120840302558</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9205,28 +9205,28 @@
         <v>-0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.02642850495499472</v>
+        <v>-0.06768550786817001</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.004260049307465665</v>
+        <v>0.0102279727609073</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.02466206814603156</v>
+        <v>0.0434279463563787</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>-0</v>
@@ -9235,10 +9235,10 @@
         <v>0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.007458122977956908</v>
+        <v>-0.02329687057131838</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,64 +9247,64 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.0006786419483999593</v>
+        <v>0.09595889419233883</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.02317395392696445</v>
+        <v>0.06895874122066736</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.02001764049277187</v>
+        <v>-0.06890462123330202</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.007080366347209785</v>
+        <v>0.007130038803875816</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.02416010117408244</v>
+        <v>0.05925594604669742</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE16" t="n">
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.0165175536301642</v>
+        <v>-0.02047642494833745</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.02586406644362148</v>
+        <v>-0.0955212851507726</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.007079006932766817</v>
+        <v>0.05717134555870657</v>
       </c>
       <c r="DK16" t="n">
         <v>-0</v>
@@ -9319,34 +9319,34 @@
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.006781662007949998</v>
+        <v>-0.01344923766967236</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01788579728714385</v>
+        <v>-0.06585807634744219</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.008324347205209054</v>
+        <v>0.04062000882953606</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.04172477594334412</v>
+        <v>0.01409270176827759</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
@@ -9355,40 +9355,40 @@
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.01874645529140154</v>
+        <v>-0.04495200666367587</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.01161392802629558</v>
+        <v>0.02367818620302259</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.03046951967564806</v>
+        <v>-0.0390110693064973</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI16" t="n">
         <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.007045408054830694</v>
+        <v>0.0195793374590973</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.02425673387379929</v>
+        <v>0.003155725963663686</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
@@ -9397,22 +9397,22 @@
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.009827443909543555</v>
+        <v>-0.01233942355497336</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.006522964190888415</v>
+        <v>0.002364471830275962</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.005877779717316957</v>
+        <v>0.07983689841976564</v>
       </c>
       <c r="EU16" t="n">
         <v>0</v>
@@ -9421,58 +9421,58 @@
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.02103444219215935</v>
+        <v>-0.07685724802631483</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.01105978135877241</v>
+        <v>-0.005280458213963516</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.02903842041241254</v>
+        <v>0.03741108932936915</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.02336827631257295</v>
+        <v>0.1320640040835579</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.007236959987348461</v>
+        <v>-0.06257672375785009</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.01423656440811494</v>
+        <v>0.09404238662467804</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,55 +9481,55 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.005684979372316152</v>
+        <v>0.03684908639976929</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.02068423631315137</v>
+        <v>-0.06688913564655337</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.008726168620858605</v>
+        <v>-0.02252705824033941</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.0007518997508050961</v>
+        <v>-0.02870145490651067</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.008598198111988859</v>
+        <v>0.05832435713111219</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -9537,22 +9537,22 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5813243576885919</v>
+        <v>0.2140285096176106</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2206994894259464</v>
+        <v>-0.1620589676380244</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.07252604116140544</v>
+        <v>-0.02155504363874082</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -9564,16 +9564,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3569896699763817</v>
+        <v>0.2200142189123537</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2071593044659994</v>
+        <v>-0.1873635397933112</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.06665193226483974</v>
+        <v>-0.05862286185882077</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9591,133 +9591,133 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1249257747491337</v>
+        <v>0.0419436702193044</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.02355359952968996</v>
+        <v>-0.04274917345693774</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1110585249895825</v>
+        <v>-0.06472007069701625</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.03518189401378809</v>
+        <v>-0.06367616607114929</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.001077197337505317</v>
+        <v>-0.09847575367799817</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.01199750620940051</v>
+        <v>-0.06272299148959753</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.02150029386535373</v>
+        <v>0.07433204246326182</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.07057779939127096</v>
+        <v>-0.08785537101436791</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.05701923833431558</v>
+        <v>0.02079676264153217</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.5025124717972149</v>
+        <v>0.2090295542808654</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.02190687204463071</v>
+        <v>-0.06907948039734998</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1062287837388484</v>
+        <v>-0.1349588446713372</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.05983557086145651</v>
+        <v>-0.006550267135237544</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.206401151511279</v>
+        <v>-0.04782362833881886</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.1324715814607463</v>
+        <v>-0.004683968080500749</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,16 +9726,16 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.1583608267954703</v>
+        <v>0.00985824007954289</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.06112346576495088</v>
+        <v>0.04943320495001371</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.1992811513780138</v>
+        <v>0.05537617600038331</v>
       </c>
       <c r="BQ17" t="n">
         <v>-0</v>
@@ -9747,52 +9747,52 @@
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.1642993282539399</v>
+        <v>0.100733829253074</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.00212385463958162</v>
+        <v>-0.07995804066813421</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.05186101998581934</v>
+        <v>-0.01379174993439551</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.1117997928943105</v>
+        <v>-0.05996584714168852</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.004731869409532737</v>
+        <v>0.08514574165648765</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.01736936817915298</v>
+        <v>0.01058404678934329</v>
       </c>
       <c r="CI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ17" t="n">
         <v>0</v>
@@ -9804,28 +9804,28 @@
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.01068045688767222</v>
+        <v>-0.04769037141456656</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.1212422279322519</v>
+        <v>0.1385422200882636</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.111511230346818</v>
+        <v>0.02258257277255022</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
         <v>-0</v>
@@ -9834,43 +9834,43 @@
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.07739655762398902</v>
+        <v>-0.05732712844428756</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.04811590700710487</v>
+        <v>0.08833178482097961</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.02580664016101752</v>
+        <v>0.0198981360659001</v>
       </c>
       <c r="DA17" t="n">
         <v>0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.04762004907848635</v>
+        <v>-0.04878290384335696</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.06158190868520314</v>
+        <v>0.02118362689974244</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.03325450218359662</v>
+        <v>-0.02851880885602913</v>
       </c>
       <c r="DJ17" t="n">
         <v>-0</v>
@@ -9885,28 +9885,28 @@
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.08595384562032246</v>
+        <v>-0.03986818059830998</v>
       </c>
       <c r="DP17" t="n">
         <v>0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.004288517580598857</v>
+        <v>-0.01274351768998171</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.04198705855323432</v>
+        <v>-0.008623886766911514</v>
       </c>
       <c r="DS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
         <v>0</v>
@@ -9915,19 +9915,19 @@
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.1167563420244909</v>
+        <v>0.01292444487786096</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.01496696756663771</v>
+        <v>0.07666161945503448</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.04456813443004735</v>
+        <v>-0.04614350998299566</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
@@ -9936,85 +9936,85 @@
         <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.09548131834028595</v>
+        <v>-0.03981101147317752</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.01601281293796111</v>
+        <v>0.06031493344383522</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.06163472843071433</v>
+        <v>0.0539949693488185</v>
       </c>
       <c r="EK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.002499175480886409</v>
+        <v>-0.001278404828596262</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>-0.008703273729854412</v>
+        <v>0.0536409264515467</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.02338733960352353</v>
+        <v>-0.02447356474861561</v>
       </c>
       <c r="ET17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
         <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.07610308434348266</v>
+        <v>-0.06241191557339784</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.003396274756274597</v>
+        <v>0.1073159268335619</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.009733433973316323</v>
+        <v>-0.001413111506326092</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF17" t="n">
         <v>0</v>
@@ -10023,16 +10023,16 @@
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.08058879776498599</v>
+        <v>0.09852467641528358</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.00641199004439016</v>
+        <v>0.06408232173334319</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.05149287077661532</v>
+        <v>-0.02704003936808545</v>
       </c>
       <c r="FL17" t="n">
         <v>-0</v>
@@ -10044,28 +10044,28 @@
         <v>-0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.05826825703075308</v>
+        <v>0.0413641989796804</v>
       </c>
       <c r="FR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.01198161159234575</v>
+        <v>0.1080327000434127</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.08264678248169126</v>
+        <v>-0.04951974498167596</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
         <v>-0</v>
@@ -10074,28 +10074,28 @@
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.07896142475276292</v>
+        <v>-0.009315359319941627</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.132879181348353</v>
+        <v>0.02432941102280659</v>
       </c>
       <c r="GC17" t="n">
         <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>-0</v>
@@ -10106,7 +10106,7 @@
         <v>-0</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.9555535467151666</v>
+        <v>-0.3533002079028263</v>
       </c>
       <c r="C18" t="n">
         <v>-0</v>
@@ -10115,13 +10115,13 @@
         <v>-0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.125218400974022</v>
+        <v>0.1283585112200805</v>
       </c>
       <c r="F18" t="n">
-        <v>1.367357707842619</v>
+        <v>0.5584751156981523</v>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10130,10 +10130,10 @@
         <v>-0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.774964630484031</v>
+        <v>-0.541171906617035</v>
       </c>
       <c r="L18" t="n">
         <v>-0</v>
@@ -10142,10 +10142,10 @@
         <v>-0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.08593641735988644</v>
+        <v>0.1752026624678895</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9513003471920908</v>
+        <v>0.5923779444512263</v>
       </c>
       <c r="P18" t="n">
         <v>-0</v>
@@ -10154,52 +10154,52 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.08767046504047085</v>
+        <v>-0.1037396363313098</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V18" t="n">
         <v>-0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.255751955271979</v>
+        <v>0.1335945490888242</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1525096043649294</v>
+        <v>0.09325074991965922</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.0365806195114871</v>
+        <v>0.01487611978664904</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>-0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.193784556180716</v>
+        <v>0.1787230598845983</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.136856267870123</v>
+        <v>-0.03626830346152047</v>
       </c>
       <c r="AH18" t="n">
         <v>-0</v>
@@ -10208,13 +10208,13 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK18" t="n">
         <v>-0</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.106279521899657</v>
+        <v>-0.06010904197959577</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
@@ -10223,13 +10223,13 @@
         <v>-0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.04253660065987656</v>
+        <v>0.02677046183071049</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.2565428489980843</v>
+        <v>0.08494498845276764</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -10238,37 +10238,37 @@
         <v>-0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>-0.6172717534061476</v>
+        <v>-0.6818937221120029</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW18" t="n">
         <v>-0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.2705298344331309</v>
+        <v>0.08214408961948282</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.8951261879568482</v>
+        <v>0.3424625867890921</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD18" t="n">
-        <v>-0.2789822097179999</v>
+        <v>0.1842094098689358</v>
       </c>
       <c r="BE18" t="n">
         <v>-0</v>
@@ -10277,10 +10277,10 @@
         <v>-0</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.1325191045465678</v>
+        <v>0.1129157665574255</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.341250828619303</v>
+        <v>0.03919596040593061</v>
       </c>
       <c r="BI18" t="n">
         <v>-0</v>
@@ -10289,52 +10289,52 @@
         <v>0</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM18" t="n">
-        <v>-0.3118136950174849</v>
+        <v>-0.1794629255678651</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>-0.1115819091716627</v>
+        <v>-0.1475984104975039</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.02734112332789938</v>
+        <v>-0.1335762630905444</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT18" t="n">
         <v>-0</v>
       </c>
       <c r="BU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>-0.3985786115602167</v>
+        <v>-0.3068061675727154</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
         <v>-0</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.08213475946453966</v>
+        <v>0.007568137216141973</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.3854074217352527</v>
+        <v>0.2026751854423259</v>
       </c>
       <c r="CA18" t="n">
         <v>0</v>
@@ -10349,22 +10349,22 @@
         <v>0</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.1664524391208402</v>
+        <v>0.1047180473073995</v>
       </c>
       <c r="CF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG18" t="n">
         <v>0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.02167547117803665</v>
+        <v>-0.06922820647789719</v>
       </c>
       <c r="CI18" t="n">
-        <v>-0.2299443871168447</v>
+        <v>-0.147455566111848</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK18" t="n">
         <v>-0</v>
@@ -10376,7 +10376,7 @@
         <v>-0</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.04461671217303093</v>
+        <v>0.1984712269322874</v>
       </c>
       <c r="CO18" t="n">
         <v>0</v>
@@ -10385,16 +10385,16 @@
         <v>0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.228126154058156</v>
+        <v>-0.03158455191819531</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.02552499353990513</v>
+        <v>0.007798438236878267</v>
       </c>
       <c r="CS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU18" t="n">
         <v>0</v>
@@ -10403,22 +10403,22 @@
         <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.1385072600200643</v>
+        <v>0.09824052826777047</v>
       </c>
       <c r="CX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY18" t="n">
         <v>-0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.02132292414102758</v>
+        <v>-0.06746262848456921</v>
       </c>
       <c r="DA18" t="n">
-        <v>-0.2484861342905257</v>
+        <v>-0.1692339418255203</v>
       </c>
       <c r="DB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC18" t="n">
         <v>0</v>
@@ -10427,49 +10427,49 @@
         <v>-0</v>
       </c>
       <c r="DE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.2395404847638643</v>
+        <v>0.1115678090768223</v>
       </c>
       <c r="DG18" t="n">
         <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.2939200123485097</v>
+        <v>0.1141473448940579</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.003028341296505732</v>
+        <v>-0.01179284602614442</v>
       </c>
       <c r="DK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL18" t="n">
         <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN18" t="n">
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.0383313838986394</v>
+        <v>-0.01895351364657017</v>
       </c>
       <c r="DP18" t="n">
         <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR18" t="n">
-        <v>-0.05398197819079133</v>
+        <v>0.05685659910989263</v>
       </c>
       <c r="DS18" t="n">
-        <v>-0.1432666533808165</v>
+        <v>-0.1433323187563683</v>
       </c>
       <c r="DT18" t="n">
         <v>0</v>
@@ -10478,25 +10478,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.1286753574867674</v>
+        <v>0.1170513750861301</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.1064783166537736</v>
+        <v>0.01348738087853794</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.1019188304297612</v>
+        <v>-0.01317884500368069</v>
       </c>
       <c r="EC18" t="n">
         <v>0</v>
@@ -10505,31 +10505,31 @@
         <v>-0</v>
       </c>
       <c r="EE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.1043654927206298</v>
+        <v>0.04332721976141553</v>
       </c>
       <c r="EH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>-0.05874249858191107</v>
+        <v>-0.03134420921569546</v>
       </c>
       <c r="EK18" t="n">
-        <v>-0.1857520990892341</v>
+        <v>-0.06111526526512318</v>
       </c>
       <c r="EL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN18" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
         <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.09569497589024525</v>
+        <v>0.04958670946011468</v>
       </c>
       <c r="EQ18" t="n">
         <v>0</v>
@@ -10547,25 +10547,25 @@
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.008703144792652799</v>
+        <v>-0.05905340457962627</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.002452998929811908</v>
+        <v>0.147769981378384</v>
       </c>
       <c r="EU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV18" t="n">
         <v>-0</v>
       </c>
       <c r="EW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX18" t="n">
         <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.1321316036627264</v>
+        <v>0.121034147440436</v>
       </c>
       <c r="EZ18" t="n">
         <v>0</v>
@@ -10574,13 +10574,13 @@
         <v>0</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.0492038552903505</v>
+        <v>-0.02740460909330773</v>
       </c>
       <c r="FC18" t="n">
-        <v>-0.2257031928486266</v>
+        <v>-0.1478208679297496</v>
       </c>
       <c r="FD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE18" t="n">
         <v>-0</v>
@@ -10592,7 +10592,7 @@
         <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.0147379497163268</v>
+        <v>-0.083775260201131</v>
       </c>
       <c r="FI18" t="n">
         <v>-0</v>
@@ -10601,10 +10601,10 @@
         <v>0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.0152848375093764</v>
+        <v>0.06975006930206748</v>
       </c>
       <c r="FL18" t="n">
-        <v>-0.1619539842595783</v>
+        <v>-0.08667578970839165</v>
       </c>
       <c r="FM18" t="n">
         <v>-0</v>
@@ -10613,52 +10613,52 @@
         <v>0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.01578419601728682</v>
+        <v>0.03449667826520292</v>
       </c>
       <c r="FR18" t="n">
         <v>0</v>
       </c>
       <c r="FS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.1171188790328716</v>
+        <v>0.1502937213230972</v>
       </c>
       <c r="FU18" t="n">
-        <v>-0.1960341491796673</v>
+        <v>0.1790597287533324</v>
       </c>
       <c r="FV18" t="n">
         <v>0</v>
       </c>
       <c r="FW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX18" t="n">
         <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.03153613549508923</v>
+        <v>0.04596655001965494</v>
       </c>
       <c r="GA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB18" t="n">
         <v>0</v>
       </c>
       <c r="GC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.1265500728807336</v>
+        <v>-0.07512856400080017</v>
       </c>
       <c r="GE18" t="n">
         <v>0</v>
@@ -10667,12 +10667,12 @@
         <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.1579309657606398</v>
+        <v>0.3395026015448797</v>
       </c>
       <c r="B19" t="n">
         <v>-0</v>
@@ -10684,13 +10684,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.002062509904998334</v>
+        <v>5.031951349659168e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1440615630925162</v>
+        <v>-0.1375987411705322</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H19" t="n">
         <v>-0</v>
@@ -10699,10 +10699,10 @@
         <v>-0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1233197493734981</v>
+        <v>0.3116027338226297</v>
       </c>
       <c r="K19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -10711,40 +10711,40 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.01531587392365156</v>
+        <v>-0.150273118281725</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1081050802752104</v>
+        <v>-0.2051877834276671</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>-0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.02037933682254647</v>
+        <v>-0.03456355767217349</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.01996452474508568</v>
+        <v>0.03227011457483955</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.04084137734115367</v>
+        <v>-0.02549758402511463</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -10753,7 +10753,7 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.02430063161776922</v>
+        <v>0.02669716617710559</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -10762,16 +10762,16 @@
         <v>-0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.01015817872023107</v>
+        <v>-0.05909778891144793</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.01878738735423515</v>
+        <v>0.09647983708093698</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -10780,49 +10780,49 @@
         <v>-0</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.02660686185573689</v>
+        <v>0.0412893496044962</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.02169268939640987</v>
+        <v>0.0375131562887402</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.01854946827056193</v>
+        <v>0.02135514439549495</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.08048047464782969</v>
+        <v>0.1256104307242744</v>
       </c>
       <c r="AU19" t="n">
         <v>-0</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>-0.04839249995448342</v>
+        <v>-0.005310389798564583</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0.06952785216480141</v>
+        <v>-0.1122869878121553</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
@@ -10834,22 +10834,22 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.03912543410912706</v>
+        <v>0.1127501272889474</v>
       </c>
       <c r="BD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.01978195399292558</v>
+        <v>-0.02715267139134464</v>
       </c>
       <c r="BH19" t="n">
-        <v>-0.06206423708270363</v>
+        <v>0.07047526441116896</v>
       </c>
       <c r="BI19" t="n">
         <v>0</v>
@@ -10861,52 +10861,52 @@
         <v>-0</v>
       </c>
       <c r="BL19" t="n">
-        <v>-0.0009339359621069522</v>
+        <v>-0.05993342263963333</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN19" t="n">
         <v>-0</v>
       </c>
       <c r="BO19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>-0.02317516172825269</v>
+        <v>-0.154309370633205</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.005510130071806345</v>
+        <v>0.04613003827270573</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
         <v>0</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU19" t="n">
-        <v>0.04272999750064014</v>
+        <v>0.05848808710617623</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
       </c>
       <c r="BW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>-0.009650314691324205</v>
+        <v>-0.09802971521207755</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0.04152762580788315</v>
+        <v>-0.05682214246312278</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB19" t="n">
         <v>0</v>
@@ -10915,25 +10915,25 @@
         <v>0</v>
       </c>
       <c r="CD19" t="n">
-        <v>-0.02950793266379362</v>
+        <v>-0.07974596159020114</v>
       </c>
       <c r="CE19" t="n">
         <v>0</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.003119697467546191</v>
+        <v>0.0357180108896093</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.03210219308404522</v>
+        <v>0.04092891997628759</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
         <v>0</v>
@@ -10942,34 +10942,34 @@
         <v>0</v>
       </c>
       <c r="CM19" t="n">
-        <v>-0.003887501391928498</v>
+        <v>-0.02830392360850174</v>
       </c>
       <c r="CN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>0.03765491202443046</v>
+        <v>0.2036461302788827</v>
       </c>
       <c r="CR19" t="n">
-        <v>0.006480832166932005</v>
+        <v>-0.09116718205522145</v>
       </c>
       <c r="CS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT19" t="n">
         <v>-0</v>
       </c>
       <c r="CU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV19" t="n">
-        <v>-0.02748902616889345</v>
+        <v>-0.08828320624860436</v>
       </c>
       <c r="CW19" t="n">
         <v>-0</v>
@@ -10981,64 +10981,64 @@
         <v>-0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0.006438022574553357</v>
+        <v>0.03822012176900542</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.02715361035583444</v>
+        <v>0.05532172916999099</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
         <v>-0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE19" t="n">
-        <v>-0.0003229328054935052</v>
+        <v>-0.002293309109758107</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.003639453667989901</v>
+        <v>-0.01222602261182273</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.02504617243515229</v>
+        <v>0.02021265861381678</v>
       </c>
       <c r="DK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN19" t="n">
-        <v>-0.01165685776789508</v>
+        <v>-0.03832120989353538</v>
       </c>
       <c r="DO19" t="n">
         <v>0</v>
       </c>
       <c r="DP19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ19" t="n">
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.005441236865295638</v>
+        <v>-0.008711802460212317</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.0332996145674316</v>
+        <v>0.07290878640664013</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
@@ -11047,13 +11047,13 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW19" t="n">
-        <v>-0.009573496140179692</v>
+        <v>-0.0007401236901088175</v>
       </c>
       <c r="DX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY19" t="n">
         <v>-0</v>
@@ -11062,37 +11062,37 @@
         <v>0</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.006375622279817778</v>
+        <v>0.2134900589116847</v>
       </c>
       <c r="EB19" t="n">
-        <v>0.01023388080882538</v>
+        <v>0.04103592815788894</v>
       </c>
       <c r="EC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED19" t="n">
         <v>-0</v>
       </c>
       <c r="EE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF19" t="n">
-        <v>-0.02497385562171606</v>
+        <v>-0.003985438414683904</v>
       </c>
       <c r="EG19" t="n">
         <v>0</v>
       </c>
       <c r="EH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI19" t="n">
         <v>0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.01184644214678479</v>
+        <v>-0.01278295147820323</v>
       </c>
       <c r="EK19" t="n">
-        <v>0.01918113999791521</v>
+        <v>0.05479012062848418</v>
       </c>
       <c r="EL19" t="n">
         <v>-0</v>
@@ -11101,10 +11101,10 @@
         <v>0</v>
       </c>
       <c r="EN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO19" t="n">
-        <v>0.008675408975855503</v>
+        <v>0.06427839405037968</v>
       </c>
       <c r="EP19" t="n">
         <v>0</v>
@@ -11113,13 +11113,13 @@
         <v>-0</v>
       </c>
       <c r="ER19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES19" t="n">
-        <v>-0.01691449656249501</v>
+        <v>0.04933995629361376</v>
       </c>
       <c r="ET19" t="n">
-        <v>0.004402519263486972</v>
+        <v>0.01532645209140761</v>
       </c>
       <c r="EU19" t="n">
         <v>0</v>
@@ -11128,10 +11128,10 @@
         <v>0</v>
       </c>
       <c r="EW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX19" t="n">
-        <v>-0.02585173574717364</v>
+        <v>-0.07920273255707154</v>
       </c>
       <c r="EY19" t="n">
         <v>0</v>
@@ -11143,13 +11143,13 @@
         <v>0</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.01051616013090552</v>
+        <v>0.03974485033865238</v>
       </c>
       <c r="FC19" t="n">
-        <v>0.02741666215149489</v>
+        <v>0.05466035745958849</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
         <v>0</v>
@@ -11158,7 +11158,7 @@
         <v>0</v>
       </c>
       <c r="FG19" t="n">
-        <v>-0.01411831644716053</v>
+        <v>-0.09904359305157003</v>
       </c>
       <c r="FH19" t="n">
         <v>-0</v>
@@ -11170,55 +11170,55 @@
         <v>-0</v>
       </c>
       <c r="FK19" t="n">
-        <v>0.001086091336808162</v>
+        <v>0.0004306745533487138</v>
       </c>
       <c r="FL19" t="n">
-        <v>-0.0007414155784733195</v>
+        <v>0.01996063254442207</v>
       </c>
       <c r="FM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP19" t="n">
-        <v>-0.01406957366843699</v>
+        <v>-0.1517896920271032</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.005908819036342376</v>
+        <v>0.007813253424440746</v>
       </c>
       <c r="FU19" t="n">
-        <v>0.03298655549764764</v>
+        <v>0.1436246770624217</v>
       </c>
       <c r="FV19" t="n">
         <v>-0</v>
       </c>
       <c r="FW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY19" t="n">
-        <v>0.002011294494542216</v>
+        <v>0.02881906034122671</v>
       </c>
       <c r="FZ19" t="n">
         <v>-0</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
         <v>-0</v>
@@ -11227,13 +11227,13 @@
         <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>0.006441024939235725</v>
+        <v>0.03089850698238748</v>
       </c>
       <c r="GE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG19" t="n">
         <v>0</v>
